--- a/Modelo/datos/Intermedias/instance_template_v4.xlsx
+++ b/Modelo/datos/Intermedias/instance_template_v4.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21a7d57e8591b932/Escritorio/CICS/2025/Tesis/Objetivos de Aprendizaje/Modelo/datos/Intermedias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{18D5E893-1FC6-4704-B72F-E449960497A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE96B381-AE30-4708-9BE6-C3C74770EE5E}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{18D5E893-1FC6-4704-B72F-E449960497A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF2A32D4-2295-4746-92A9-82B9022B98CC}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="meta" sheetId="1" r:id="rId1"/>
-    <sheet name="concepts" sheetId="2" r:id="rId2"/>
-    <sheet name="Hoja1" sheetId="4" r:id="rId3"/>
-    <sheet name="precedence" sheetId="3" r:id="rId4"/>
+    <sheet name="README" sheetId="5" r:id="rId1"/>
+    <sheet name="meta" sheetId="1" r:id="rId2"/>
+    <sheet name="concepts" sheetId="2" r:id="rId3"/>
+    <sheet name="Hoja1" sheetId="4" r:id="rId4"/>
+    <sheet name="precedence" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="52">
   <si>
     <t>parameter</t>
   </si>
@@ -180,6 +181,18 @@
   </si>
   <si>
     <t>Comisiones_AFP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En hoja concepts estan los 36 conceptos con su tiempo p calculado como 200 palabras por minuto y dividido entre 10 y redondeado y w que considera decendentes, foundation y betwuennes (0,55 - 0,3 - 0,15 respectivamente) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En hoja Hoja1 es una copia de concepts, pero con p = 200 palabras por min </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En hoja meta estan los parámetros de la función repensados con el propio problema, con el tiempo h = 150 (representando 25 min) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En hoja precedence estan las precedencias considerando la matriz A min (enlaces transitivos eliminados) </t>
   </si>
 </sst>
 </file>
@@ -531,6 +544,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD8B0B17-C124-4D15-AABA-A25EFA5CE59F}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -584,7 +627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1118,7 +1161,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48614C93-FFB4-4246-BDEF-23A780D5BE81}">
   <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1535,7 +1578,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
